--- a/src/app/modules/dashboard/excel_files/whole-food-plant-based-stir-fry-recipes.xlsx
+++ b/src/app/modules/dashboard/excel_files/whole-food-plant-based-stir-fry-recipes.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stir-fry', 'bowls', 'noodles']</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
